--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>194460</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>61330</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.74500000476837</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.74500000476837</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>6260</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>52839</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>60062</v>
+        <v>42404</v>
       </c>
       <c r="C2715" t="n">
-        <v>1.67999994754791</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="D2715" t="n">
         <v>1.62000000476837</v>
       </c>
       <c r="E2715" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="F2715" t="n">
         <v>1.62000000476837</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>1.6599999666214</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,13 +62819,13 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>29563</v>
+        <v>60062</v>
       </c>
       <c r="C2716" t="n">
-        <v>1.68499994277954</v>
+        <v>1.67999994754791</v>
       </c>
       <c r="D2716" t="n">
         <v>1.62000000476837</v>
@@ -62834,7 +62834,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="F2716" t="n">
-        <v>1.66499996185303</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>54190</v>
+        <v>29563</v>
       </c>
       <c r="C2717" t="n">
-        <v>1.69000005722046</v>
+        <v>1.68499994277954</v>
       </c>
       <c r="D2717" t="n">
-        <v>1.6599999666214</v>
+        <v>1.62000000476837</v>
       </c>
       <c r="E2717" t="n">
-        <v>1.66999995708466</v>
+        <v>1.62000000476837</v>
       </c>
       <c r="F2717" t="n">
-        <v>1.66999995708466</v>
+        <v>1.66499996185303</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>93121</v>
+        <v>54190</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.70000004768372</v>
+        <v>1.69000005722046</v>
       </c>
       <c r="D2718" t="n">
-        <v>1.64499998092651</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="E2718" t="n">
-        <v>1.6599999666214</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="F2718" t="n">
-        <v>1.66499996185303</v>
+        <v>1.66999995708466</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>194460</v>
+        <v>93121</v>
       </c>
       <c r="C2719" t="n">
-        <v>1.72000002861023</v>
+        <v>1.70000004768372</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.6599999666214</v>
+        <v>1.64499998092651</v>
       </c>
       <c r="E2719" t="n">
         <v>1.6599999666214</v>
       </c>
       <c r="F2719" t="n">
-        <v>1.70000004768372</v>
+        <v>1.66499996185303</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>61330</v>
+        <v>194460</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.74500000476837</v>
+        <v>1.72000002861023</v>
       </c>
       <c r="D2720" t="n">
         <v>1.6599999666214</v>
       </c>
       <c r="E2720" t="n">
-        <v>1.74500000476837</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="F2720" t="n">
-        <v>1.6599999666214</v>
+        <v>1.70000004768372</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>6260</v>
+        <v>61330</v>
       </c>
       <c r="C2721" t="n">
-        <v>1.69500005245209</v>
+        <v>1.74500000476837</v>
       </c>
       <c r="D2721" t="n">
-        <v>1.64499998092651</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="E2721" t="n">
-        <v>1.69500005245209</v>
+        <v>1.74500000476837</v>
       </c>
       <c r="F2721" t="n">
-        <v>1.64499998092651</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,10 +62957,10 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>52839</v>
+        <v>6260</v>
       </c>
       <c r="C2722" t="n">
         <v>1.69500005245209</v>
@@ -62969,12 +62969,35 @@
         <v>1.64499998092651</v>
       </c>
       <c r="E2722" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="F2722" t="n">
         <v>1.64499998092651</v>
       </c>
-      <c r="F2722" t="n">
-        <v>1.66999995708466</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>63343</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -71210,7 +71210,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="D2725" t="n">
-        <v>1.66999995708466</v>
+        <v>1.66499996185303</v>
       </c>
       <c r="E2725" t="n">
         <v>1.70000004768372</v>
@@ -71222,6 +71222,32 @@
         <v>1.66499996185303</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>81589</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>1.74500000476837</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>1.67499995231628</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>1.74500000476837</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -71251,6 +71251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>54886</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>32739</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.65499997138977</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -71288,7 +71288,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="D2728" t="n">
-        <v>1.64999997615814</v>
+        <v>1.62999999523163</v>
       </c>
       <c r="E2728" t="n">
         <v>1.65499997138977</v>
@@ -71300,6 +71300,32 @@
         <v>1.62999999523163</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>51447</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.60500001907349</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>47145</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.69000005722046</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.63499999046326</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>15408</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.66999995708466</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.62000000476837</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>48250</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.63499999046326</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>1.6599999666214</v>
       </c>
       <c r="D2737" t="n">
-        <v>1.63499999046326</v>
+        <v>1.62999999523163</v>
       </c>
       <c r="E2737" t="n">
         <v>1.6599999666214</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.62999999523163</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>74968</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.66999995708466</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.66499996185303</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>62221</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.67499995231628</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>25014</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -71667,6 +71667,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>39882</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>1.64499998092651</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -71675,7 +71675,7 @@
         <v>39882</v>
       </c>
       <c r="C2743" t="n">
-        <v>1.66999995708466</v>
+        <v>1.69000005722046</v>
       </c>
       <c r="D2743" t="n">
         <v>1.64499998092651</v>
@@ -71690,6 +71690,32 @@
         <v>1.69000005722046</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>22244</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.65499997138977</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -79954,6 +79954,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>1.7150000333786</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>1.66499996185303</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>156214</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.66499996185303</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>52257</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>1.67499995231628</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>1.67499995231628</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>26003</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -80026,7 +80026,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="E2747" t="n">
-        <v>1.67999994754791</v>
+        <v>1.67499995231628</v>
       </c>
       <c r="F2747" t="n">
         <v>1.67499995231628</v>
@@ -80038,6 +80038,35 @@
         <v>26003</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>81760</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -80070,6 +80070,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>1.67499995231628</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>22272</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>146060</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -80128,6 +80128,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>18460</v>
+      </c>
+      <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -80157,6 +80157,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>1.70500004291534</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>255963</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -80186,6 +80186,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>1.94500005245209</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>634123</v>
+      </c>
+      <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SSL.MI.xlsx
+++ b/data/SSL.MI.xlsx
@@ -80215,6 +80215,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>1.89499998092651</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>1.89499998092651</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>415943</v>
+      </c>
+      <c r="I2754" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
